--- a/teams.xlsx
+++ b/teams.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>Mumbai Indians</t>
   </si>
@@ -60,9 +60,6 @@
     <t>Pune Warriors</t>
   </si>
   <si>
-    <t>Kolkata Knight Riders</t>
-  </si>
-  <si>
     <t>Punjab Kings</t>
   </si>
   <si>
@@ -82,16 +79,41 @@
   </si>
   <si>
     <t>teams</t>
+  </si>
+  <si>
+    <t>Karachi Kings</t>
+  </si>
+  <si>
+    <t>Gujarat Lions</t>
+  </si>
+  <si>
+    <t>Kochi Tuskers</t>
+  </si>
+  <si>
+    <t>adelaide strikers</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -117,8 +139,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -420,7 +444,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A22"/>
+  <dimension ref="A1:A26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
@@ -428,116 +452,135 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="A10" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="A12" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="A13" s="2" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="A14" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+      <c r="A15" s="2" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>20</v>
-      </c>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A26" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
